--- a/Sources.xlsx
+++ b/Sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\Desktop\Poly\FED\CA2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7207FE0-6677-4022-AA66-7E0A91B54C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AFB8A1-1874-4277-9E8C-27215EB2CADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{84EF0130-A291-4C38-9D0A-9697C7EE0E25}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -72,6 +72,48 @@
   </si>
   <si>
     <t>https://whvn.cc/9o26rx</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/aldenbonecutter?igshid=1bka60l1knzgh</t>
+  </si>
+  <si>
+    <t>Alden Bonecutter</t>
+  </si>
+  <si>
+    <t>Ludovic Delot</t>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Tomorrowland_2026_Mainstage_Night_Show_Boom_Belgium.jpg</t>
+  </si>
+  <si>
+    <t>Frederic Edwin Church</t>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Twilight_in_the_Wilderness_by_Frederic_Edwin_Church_(3).jpg</t>
+  </si>
+  <si>
+    <t>Chris Stapleton</t>
+  </si>
+  <si>
+    <t>https://chrisstapleton.com/photos/</t>
+  </si>
+  <si>
+    <t>https://www.johnnycash.com/photo_gallery/live-performances/</t>
+  </si>
+  <si>
+    <t>Johnny Cash</t>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Young-Dolly-Parton.jpg</t>
+  </si>
+  <si>
+    <t>RCA Records</t>
+  </si>
+  <si>
+    <t>Virgin Records</t>
+  </si>
+  <si>
+    <t>https://covers.musichoarders.xyz/</t>
   </si>
 </sst>
 </file>
@@ -475,12 +517,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF03FA6A-0CF5-4B19-95EE-1A8CFCD6526B}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.453125" customWidth="1"/>
-    <col min="4" max="4" width="64.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="87.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -537,6 +579,109 @@
       </c>
       <c r="D4" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46229</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46229</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46229</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46229</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46229</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46229</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46229</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
